--- a/artfynd/A 42853-2022 artfynd.xlsx
+++ b/artfynd/A 42853-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42853-2022 artfynd.xlsx
+++ b/artfynd/A 42853-2022 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>131847191</v>
       </c>
       <c r="B5" t="n">
-        <v>57961</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42853-2022 artfynd.xlsx
+++ b/artfynd/A 42853-2022 artfynd.xlsx
@@ -1057,7 +1057,7 @@
         <v>131847191</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42853-2022 artfynd.xlsx
+++ b/artfynd/A 42853-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3492796</v>
+        <v>67681204</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorpet, Sura sn, Vstm</t>
+          <t>Holmtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560642.5562087535</v>
+        <v>560391</v>
       </c>
       <c r="R2" t="n">
-        <v>6618798.413187434</v>
+        <v>6618735</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-03-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-03-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,91 +756,79 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Trädholme i betesmark</t>
+          <t>Trädbärande betesmark</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15943536</v>
+        <v>67681388</v>
       </c>
       <c r="B3" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>lisjöbanvallen, Vstm</t>
+          <t>Holmtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>560120.8868478111</v>
+        <v>560348</v>
       </c>
       <c r="R3" t="n">
-        <v>6618695.079382664</v>
+        <v>6618654</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,18 +866,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Trädbärande betesmark</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Klinga</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Klinga</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -931,12 +898,7 @@
         <v>88929676</v>
       </c>
       <c r="B4" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560638.4466165185</v>
+        <v>560638</v>
       </c>
       <c r="R4" t="n">
-        <v>6618802.384615387</v>
+        <v>6618802</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1004,19 +966,9 @@
           <t>2020-11-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-11-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,32 +1006,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131847191</v>
+        <v>67667602</v>
       </c>
       <c r="B5" t="n">
-        <v>57966</v>
+        <v>89105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>806</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Luktvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hygrocybe quieta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kühner) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1087,31 +1039,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Holmtorpet, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>560270</v>
+        <v>560473</v>
       </c>
       <c r="R5" t="n">
-        <v>6618721</v>
+        <v>6618795</v>
       </c>
       <c r="S5" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,22 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:51</t>
+          <t>2017-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,21 +1095,1225 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80169064</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89105</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>806</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Luktvaxing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hygrocybe quieta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Kühner) Singer</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>560391</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618735</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Betad hagmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tom Sävström, Maj Karsten, Jesper Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88929700</v>
+      </c>
+      <c r="B7" t="n">
+        <v>88978</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ängsfingersvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Clavulinopsis corniculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff. : Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>560473</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6618795</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88929687</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89081</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>560391</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6618735</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67667684</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>560473</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6618795</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88929683</v>
+      </c>
+      <c r="B10" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>560348</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6618654</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>88929690</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89029</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4392</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ängsvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cuphophyllus pratensis s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>560391</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6618735</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>88929693</v>
+      </c>
+      <c r="B12" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>560391</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6618735</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-11-06</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Betesmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114973469</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57247</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrsjölunden, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>560077</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6618678</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131847191</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57988</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>560270</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6618721</v>
+      </c>
+      <c r="S14" t="n">
+        <v>41</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Per Helttunen</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Per Helttunen</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15943536</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>lisjöbanvallen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>560121</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6618695</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2014-06-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2014-06-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Hans Klinga</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3492796</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Holmtorpet, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>560643</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6618798</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2011-03-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2011-03-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Trädholme i betesmark</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42853-2022 artfynd.xlsx
+++ b/artfynd/A 42853-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67681204</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67681388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88929676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67667602</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80169064</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88929700</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88929687</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67667684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88929683</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88929690</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88929693</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114973469</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131847191</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2203,6 +2273,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15943536</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2314,8 +2389,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3492796</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>